--- a/research/traditional_assets/database/data/australia/australia_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_banks_regional.xlsx
@@ -588,124 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03415</v>
+        <v>0.06325</v>
       </c>
       <c r="E2">
-        <v>0.0475</v>
+        <v>0.0259</v>
       </c>
       <c r="F2">
-        <v>0.1645</v>
+        <v>0.052</v>
       </c>
       <c r="G2">
-        <v>0.0002612199653826759</v>
+        <v>0.0001746578000879758</v>
       </c>
       <c r="H2">
-        <v>0.0002612199653826759</v>
+        <v>0.0001746578000879758</v>
       </c>
       <c r="I2">
-        <v>0.0002103388590820503</v>
+        <v>0.0001203198178383833</v>
       </c>
       <c r="J2">
-        <v>0.0001489336546388439</v>
+        <v>9.401187580213994e-05</v>
       </c>
       <c r="K2">
-        <v>666.298</v>
+        <v>670.09</v>
       </c>
       <c r="L2">
-        <v>0.3026962443383412</v>
+        <v>0.288978877187535</v>
       </c>
       <c r="M2">
-        <v>190.846</v>
+        <v>332.531</v>
       </c>
       <c r="N2">
-        <v>0.02515046447298888</v>
+        <v>0.04841561035837316</v>
       </c>
       <c r="O2">
-        <v>0.286427394349075</v>
+        <v>0.4962482651584115</v>
       </c>
       <c r="P2">
-        <v>185.736</v>
+        <v>314.832</v>
       </c>
       <c r="Q2">
-        <v>0.02447704782576036</v>
+        <v>0.04583868403351067</v>
       </c>
       <c r="R2">
-        <v>0.2787581532587521</v>
+        <v>0.4698353952454148</v>
       </c>
       <c r="S2">
-        <v>5.109999999999999</v>
+        <v>17.699</v>
       </c>
       <c r="T2">
-        <v>0.02677551533697326</v>
+        <v>0.05322511284662181</v>
       </c>
       <c r="U2">
-        <v>5902.005</v>
+        <v>3953.109</v>
       </c>
       <c r="V2">
-        <v>0.7777902972653485</v>
+        <v>0.5755619327165832</v>
       </c>
       <c r="W2">
-        <v>0.09213858413589436</v>
+        <v>0.06759870287755723</v>
       </c>
       <c r="X2">
-        <v>0.05650721903212499</v>
+        <v>0.1085349644148743</v>
       </c>
       <c r="Y2">
-        <v>0.03563136510376937</v>
+        <v>-0.04093626153731711</v>
       </c>
       <c r="Z2">
-        <v>0.1303683956510031</v>
+        <v>0.08958787537393963</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03964636600905803</v>
+        <v>0.05665630611052294</v>
       </c>
       <c r="AC2">
-        <v>-0.03964636600905803</v>
+        <v>-0.0560447288633444</v>
       </c>
       <c r="AD2">
-        <v>17710.467</v>
+        <v>24280.89</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>17710.467</v>
+        <v>24280.89</v>
       </c>
       <c r="AG2">
-        <v>11808.462</v>
+        <v>20327.781</v>
       </c>
       <c r="AH2">
-        <v>0.7000561729867106</v>
+        <v>0.7795040956173763</v>
       </c>
       <c r="AI2">
-        <v>0.6535279041123091</v>
+        <v>0.7220373911259266</v>
       </c>
       <c r="AJ2">
-        <v>0.6087892990906876</v>
+        <v>0.7474536826885944</v>
       </c>
       <c r="AK2">
-        <v>0.5570612057431291</v>
+        <v>0.6850092725603687</v>
       </c>
       <c r="AL2">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.025</v>
+        <v>-0.006</v>
       </c>
       <c r="AN2">
-        <v>30800.81217391305</v>
-      </c>
-      <c r="AO2">
-        <v>16.53571428571428</v>
+        <v>59952.81481481481</v>
       </c>
       <c r="AP2">
-        <v>20536.45565217391</v>
+        <v>50192.05185185184</v>
       </c>
       <c r="AQ2">
-        <v>18.52</v>
+        <v>-46.5</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Logan Community Financial Services Limited (NSX:LCB)</t>
+          <t>Canterbury Surrey Hills Community Finance Limited (NSX:IEC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,121 +722,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00046</v>
+        <v>0.0124</v>
       </c>
       <c r="E3">
-        <v>0.334</v>
+        <v>-0.246</v>
       </c>
       <c r="G3">
-        <v>0.2046263345195729</v>
+        <v>0.1336633663366337</v>
       </c>
       <c r="H3">
-        <v>0.2046263345195729</v>
+        <v>0.1336633663366337</v>
       </c>
       <c r="I3">
-        <v>0.1647686832740214</v>
+        <v>0.09207920792079209</v>
       </c>
       <c r="J3">
-        <v>0.1228621973546171</v>
+        <v>0.06886596222647476</v>
       </c>
       <c r="K3">
-        <v>0.258</v>
+        <v>0.09</v>
       </c>
       <c r="L3">
-        <v>0.09181494661921709</v>
+        <v>0.02970297029702971</v>
       </c>
       <c r="M3">
-        <v>0.136</v>
+        <v>0.141</v>
       </c>
       <c r="N3">
-        <v>0.09927007299270073</v>
+        <v>0.1036764705882353</v>
       </c>
       <c r="O3">
-        <v>0.5271317829457365</v>
+        <v>1.566666666666667</v>
       </c>
       <c r="P3">
-        <v>0.136</v>
+        <v>0.132</v>
       </c>
       <c r="Q3">
-        <v>0.09927007299270073</v>
+        <v>0.09705882352941177</v>
       </c>
       <c r="R3">
-        <v>0.5271317829457365</v>
+        <v>1.466666666666667</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.009000000000000008</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.0638297872340426</v>
       </c>
       <c r="U3">
-        <v>0.805</v>
+        <v>0.309</v>
       </c>
       <c r="V3">
-        <v>0.5875912408759124</v>
+        <v>0.2272058823529411</v>
       </c>
       <c r="W3">
-        <v>0.1563636363636364</v>
+        <v>0.03501945525291829</v>
       </c>
       <c r="X3">
-        <v>0.05088276059278701</v>
+        <v>0.07990354529134516</v>
       </c>
       <c r="Y3">
-        <v>0.1054808757708494</v>
+        <v>-0.04488409003842687</v>
       </c>
       <c r="Z3">
-        <v>1.627099015634047</v>
+        <v>0.7593984962406016</v>
       </c>
       <c r="AA3">
-        <v>0.1999089603743335</v>
+        <v>0.05229670815694701</v>
       </c>
       <c r="AB3">
-        <v>0.03957274522819321</v>
+        <v>0.05788737193531093</v>
       </c>
       <c r="AC3">
-        <v>0.1603362151461403</v>
+        <v>-0.005590663778363925</v>
       </c>
       <c r="AD3">
-        <v>0.667</v>
+        <v>1.79</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.667</v>
+        <v>1.79</v>
       </c>
       <c r="AG3">
-        <v>-0.138</v>
+        <v>1.481</v>
       </c>
       <c r="AH3">
-        <v>0.3274423171330388</v>
+        <v>0.5682539682539682</v>
       </c>
       <c r="AI3">
-        <v>0.2578275995361423</v>
+        <v>0.4365853658536586</v>
       </c>
       <c r="AJ3">
-        <v>-0.112012987012987</v>
+        <v>0.5212953185498064</v>
       </c>
       <c r="AK3">
-        <v>-0.07744107744107745</v>
+        <v>0.3906620944341862</v>
       </c>
       <c r="AL3">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.025</v>
+        <v>-0.006</v>
       </c>
       <c r="AN3">
-        <v>1.16</v>
-      </c>
-      <c r="AO3">
-        <v>16.53571428571428</v>
+        <v>4.419753086419753</v>
       </c>
       <c r="AP3">
-        <v>-0.24</v>
+        <v>3.65679012345679</v>
       </c>
       <c r="AQ3">
-        <v>18.52</v>
+        <v>-46.5</v>
       </c>
     </row>
     <row r="4">
@@ -859,13 +853,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0394</v>
+        <v>0.0946</v>
       </c>
       <c r="E4">
-        <v>0.0172</v>
+        <v>0.0389</v>
       </c>
       <c r="F4">
-        <v>0.143</v>
+        <v>0.0679</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -880,85 +874,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>268.9</v>
+        <v>292.5</v>
       </c>
       <c r="L4">
-        <v>0.2888602427758084</v>
+        <v>0.256962136519371</v>
       </c>
       <c r="M4">
-        <v>111.81</v>
+        <v>179.2</v>
       </c>
       <c r="N4">
-        <v>0.029604427028172</v>
+        <v>0.0587637317593048</v>
       </c>
       <c r="O4">
-        <v>0.4158051320193381</v>
+        <v>0.6126495726495726</v>
       </c>
       <c r="P4">
-        <v>106.7</v>
+        <v>167.5</v>
       </c>
       <c r="Q4">
-        <v>0.02825142978182588</v>
+        <v>0.05492703721921627</v>
       </c>
       <c r="R4">
-        <v>0.3968017850502046</v>
+        <v>0.5726495726495726</v>
       </c>
       <c r="S4">
-        <v>5.109999999999999</v>
+        <v>11.69999999999999</v>
       </c>
       <c r="T4">
-        <v>0.04570253107950988</v>
+        <v>0.06529017857142851</v>
       </c>
       <c r="U4">
-        <v>1725.9</v>
+        <v>1680.6</v>
       </c>
       <c r="V4">
-        <v>0.4569741580173692</v>
+        <v>0.5511067388096409</v>
       </c>
       <c r="W4">
-        <v>0.08613068545803972</v>
+        <v>0.06459805653710247</v>
       </c>
       <c r="X4">
-        <v>0.1091877165543888</v>
+        <v>0.1331430917459325</v>
       </c>
       <c r="Y4">
-        <v>-0.02305703109634907</v>
+        <v>-0.06854503520883005</v>
       </c>
       <c r="Z4">
-        <v>0.08564016228300168</v>
+        <v>0.07069352064042131</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03964511488657857</v>
+        <v>0.05572302599774479</v>
       </c>
       <c r="AC4">
-        <v>-0.03964511488657857</v>
+        <v>-0.05572302599774479</v>
       </c>
       <c r="AD4">
-        <v>13626.3</v>
+        <v>14855.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>13626.3</v>
+        <v>14855.1</v>
       </c>
       <c r="AG4">
-        <v>11900.4</v>
+        <v>13174.5</v>
       </c>
       <c r="AH4">
-        <v>0.7829811930058438</v>
+        <v>0.8296806407291981</v>
       </c>
       <c r="AI4">
-        <v>0.7505825066237751</v>
+        <v>0.7639704596648942</v>
       </c>
       <c r="AJ4">
-        <v>0.7590896333528946</v>
+        <v>0.8120377218934911</v>
       </c>
       <c r="AK4">
-        <v>0.7243797326580799</v>
+        <v>0.7416403963071381</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -975,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BNK Banking Corporation Limited (ASX:BBC)</t>
+          <t>Bendigo and Adelaide Bank Limited (ASX:BEN)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,7 +978,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.629</v>
+        <v>0.0319</v>
+      </c>
+      <c r="E5">
+        <v>0.0259</v>
+      </c>
+      <c r="F5">
+        <v>0.0361</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -999,82 +999,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>4.24</v>
+        <v>336.3</v>
       </c>
       <c r="L5">
-        <v>0.1381107491856678</v>
+        <v>0.2873867714920527</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>153.19</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.04058013245033112</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.4555159084151055</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>147.2</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.0389933774834437</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.4377044305679452</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>5.990000000000009</v>
+      </c>
+      <c r="T5">
+        <v>0.03910176904497688</v>
       </c>
       <c r="U5">
-        <v>35.5</v>
+        <v>2175.7</v>
       </c>
       <c r="V5">
-        <v>0.3387404580152672</v>
+        <v>0.5763443708609272</v>
       </c>
       <c r="W5">
-        <v>0.05623342175066313</v>
+        <v>0.07059934921801198</v>
       </c>
       <c r="X5">
-        <v>0.05043300744503062</v>
+        <v>0.09690456325371052</v>
       </c>
       <c r="Y5">
-        <v>0.005800414305632509</v>
+        <v>-0.02630521403569855</v>
       </c>
       <c r="Z5">
-        <v>0.9651053127947187</v>
+        <v>0.120853472136159</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.03964761713153749</v>
+        <v>0.05636643172894401</v>
       </c>
       <c r="AC5">
-        <v>-0.03964761713153749</v>
+        <v>-0.05636643172894401</v>
       </c>
       <c r="AD5">
-        <v>48.5</v>
+        <v>9254.200000000001</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>48.5</v>
+        <v>9254.200000000001</v>
       </c>
       <c r="AG5">
-        <v>13</v>
+        <v>7078.500000000001</v>
       </c>
       <c r="AH5">
-        <v>0.3163731245923027</v>
+        <v>0.7102661713689252</v>
       </c>
       <c r="AI5">
-        <v>0.3358725761772853</v>
+        <v>0.6667963627455219</v>
       </c>
       <c r="AJ5">
-        <v>0.1103565365025467</v>
+        <v>0.652185930805731</v>
       </c>
       <c r="AK5">
-        <v>0.1193755739210285</v>
+        <v>0.6048500798947269</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1091,7 +1094,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bendigo and Adelaide Bank Limited (ASX:BEN)</t>
+          <t>BNK Banking Corporation Limited (ASX:BBC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1100,13 +1103,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0289</v>
-      </c>
-      <c r="E6">
-        <v>0.0475</v>
-      </c>
-      <c r="F6">
-        <v>0.186</v>
+        <v>0.218</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1121,85 +1118,82 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>392.9</v>
+        <v>41.2</v>
       </c>
       <c r="L6">
-        <v>0.3176746442432083</v>
+        <v>5.651577503429356</v>
       </c>
       <c r="M6">
-        <v>78.90000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.02129439706358631</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.200814456604734</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>78.90000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.02129439706358631</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.200814456604734</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>4139.8</v>
+        <v>96.5</v>
       </c>
       <c r="V6">
-        <v>1.117294612976358</v>
+        <v>2.275943396226415</v>
       </c>
       <c r="W6">
-        <v>0.09814648281374901</v>
+        <v>0.429614181438999</v>
       </c>
       <c r="X6">
-        <v>0.06213167747146297</v>
+        <v>0.1201653655760382</v>
       </c>
       <c r="Y6">
-        <v>0.03601480534228604</v>
+        <v>0.3094488158629608</v>
       </c>
       <c r="Z6">
-        <v>0.2067847051545702</v>
+        <v>0.07714285714285714</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04036113296391108</v>
+        <v>0.05694618049210187</v>
       </c>
       <c r="AC6">
-        <v>-0.04036113296391108</v>
+        <v>-0.05694618049210187</v>
       </c>
       <c r="AD6">
-        <v>4035</v>
+        <v>169.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>4035</v>
+        <v>169.8</v>
       </c>
       <c r="AG6">
-        <v>-104.8000000000002</v>
+        <v>73.30000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.5213043590604894</v>
+        <v>0.8001885014137606</v>
       </c>
       <c r="AI6">
-        <v>0.4586008978803205</v>
+        <v>0.5641196013289037</v>
       </c>
       <c r="AJ6">
-        <v>-0.02910787690256644</v>
+        <v>0.6335350043215212</v>
       </c>
       <c r="AK6">
-        <v>-0.02249554596775928</v>
+        <v>0.3584352078239609</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/research/traditional_assets/database/data/australia/australia_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06325</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0259</v>
+        <v>0.0412</v>
       </c>
       <c r="F2">
-        <v>0.052</v>
+        <v>0.12451</v>
       </c>
       <c r="G2">
-        <v>0.0001746578000879758</v>
+        <v>0.0004662673505254474</v>
       </c>
       <c r="H2">
-        <v>0.0001746578000879758</v>
+        <v>0.0004662673505254474</v>
       </c>
       <c r="I2">
-        <v>0.0001203198178383833</v>
+        <v>0.0004304006312542592</v>
       </c>
       <c r="J2">
-        <v>9.401187580213994e-05</v>
+        <v>0.0003111615736604396</v>
       </c>
       <c r="K2">
-        <v>670.09</v>
+        <v>451.386</v>
       </c>
       <c r="L2">
-        <v>0.288978877187535</v>
+        <v>0.1798859438327176</v>
       </c>
       <c r="M2">
-        <v>332.531</v>
+        <v>405.896</v>
       </c>
       <c r="N2">
-        <v>0.04841561035837316</v>
+        <v>0.05898356610685737</v>
       </c>
       <c r="O2">
-        <v>0.4962482651584115</v>
+        <v>0.8992215088638106</v>
       </c>
       <c r="P2">
-        <v>314.832</v>
+        <v>382.296</v>
       </c>
       <c r="Q2">
-        <v>0.04583868403351067</v>
+        <v>0.05555408623979331</v>
       </c>
       <c r="R2">
-        <v>0.4698353952454148</v>
+        <v>0.8469380973268997</v>
       </c>
       <c r="S2">
-        <v>17.699</v>
+        <v>23.6</v>
       </c>
       <c r="T2">
-        <v>0.05322511284662181</v>
+        <v>0.05814297258411022</v>
       </c>
       <c r="U2">
-        <v>3953.109</v>
+        <v>6402.26</v>
       </c>
       <c r="V2">
-        <v>0.5755619327165832</v>
+        <v>0.9303568548182014</v>
       </c>
       <c r="W2">
-        <v>0.06759870287755723</v>
+        <v>0.07874158344582562</v>
       </c>
       <c r="X2">
-        <v>0.1085349644148743</v>
+        <v>0.09389568556920296</v>
       </c>
       <c r="Y2">
-        <v>-0.04093626153731711</v>
+        <v>-0.01515410212337734</v>
       </c>
       <c r="Z2">
-        <v>0.08958787537393963</v>
+        <v>0.08405727347038969</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05665630611052294</v>
+        <v>0.04731609879768429</v>
       </c>
       <c r="AC2">
-        <v>-0.0560447288633444</v>
+        <v>-0.04516518273580228</v>
       </c>
       <c r="AD2">
-        <v>24280.89</v>
+        <v>24980.539</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>24280.89</v>
+        <v>24980.539</v>
       </c>
       <c r="AG2">
-        <v>20327.781</v>
+        <v>18578.279</v>
       </c>
       <c r="AH2">
-        <v>0.7795040956173763</v>
+        <v>0.7840217369573439</v>
       </c>
       <c r="AI2">
-        <v>0.7220373911259266</v>
+        <v>0.7326397670103303</v>
       </c>
       <c r="AJ2">
-        <v>0.7474536826885944</v>
+        <v>0.7297106429279521</v>
       </c>
       <c r="AK2">
-        <v>0.6850092725603687</v>
+        <v>0.6708326052969849</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="AM2">
-        <v>-0.006</v>
+        <v>0.001999999999999998</v>
       </c>
       <c r="AN2">
-        <v>59952.81481481481</v>
+        <v>21350.88803418804</v>
+      </c>
+      <c r="AO2">
+        <v>60.00000000000001</v>
       </c>
       <c r="AP2">
-        <v>50192.05185185184</v>
+        <v>15878.87094017094</v>
       </c>
       <c r="AQ2">
-        <v>-46.5</v>
+        <v>540.0000000000005</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Canterbury Surrey Hills Community Finance Limited (NSX:IEC)</t>
+          <t>Logan Community Financial Services Limited (NSX:LCB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,118 +725,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0124</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="E3">
-        <v>-0.246</v>
+        <v>0.5</v>
       </c>
       <c r="G3">
-        <v>0.1336633663366337</v>
+        <v>0.3556231003039513</v>
       </c>
       <c r="H3">
-        <v>0.1336633663366337</v>
+        <v>0.3556231003039513</v>
       </c>
       <c r="I3">
-        <v>0.09207920792079209</v>
+        <v>0.3282674772036475</v>
       </c>
       <c r="J3">
-        <v>0.06886596222647476</v>
+        <v>0.2483521737645573</v>
       </c>
       <c r="K3">
-        <v>0.09</v>
+        <v>0.606</v>
       </c>
       <c r="L3">
-        <v>0.02970297029702971</v>
+        <v>0.1841945288753799</v>
       </c>
       <c r="M3">
-        <v>0.141</v>
+        <v>0.106</v>
       </c>
       <c r="N3">
-        <v>0.1036764705882353</v>
+        <v>0.075177304964539</v>
       </c>
       <c r="O3">
-        <v>1.566666666666667</v>
+        <v>0.1749174917491749</v>
       </c>
       <c r="P3">
-        <v>0.132</v>
+        <v>0.106</v>
       </c>
       <c r="Q3">
-        <v>0.09705882352941177</v>
+        <v>0.075177304964539</v>
       </c>
       <c r="R3">
-        <v>1.466666666666667</v>
+        <v>0.1749174917491749</v>
       </c>
       <c r="S3">
-        <v>0.009000000000000008</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.0638297872340426</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>0.309</v>
+        <v>1.36</v>
       </c>
       <c r="V3">
-        <v>0.2272058823529411</v>
+        <v>0.9645390070921988</v>
       </c>
       <c r="W3">
-        <v>0.03501945525291829</v>
+        <v>0.3293478260869565</v>
       </c>
       <c r="X3">
-        <v>0.07990354529134516</v>
+        <v>0.05452919371667127</v>
       </c>
       <c r="Y3">
-        <v>-0.04488409003842687</v>
+        <v>0.2748186323702853</v>
       </c>
       <c r="Z3">
-        <v>0.7593984962406016</v>
+        <v>2.141927083333333</v>
       </c>
       <c r="AA3">
-        <v>0.05229670815694701</v>
+        <v>0.5319522471910113</v>
       </c>
       <c r="AB3">
-        <v>0.05788737193531093</v>
+        <v>0.05122207452287392</v>
       </c>
       <c r="AC3">
-        <v>-0.005590663778363925</v>
+        <v>0.4807301726681374</v>
       </c>
       <c r="AD3">
-        <v>1.79</v>
+        <v>0.339</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.79</v>
+        <v>0.339</v>
       </c>
       <c r="AG3">
-        <v>1.481</v>
+        <v>-1.021</v>
       </c>
       <c r="AH3">
-        <v>0.5682539682539682</v>
+        <v>0.1938250428816467</v>
       </c>
       <c r="AI3">
-        <v>0.4365853658536586</v>
+        <v>0.1294387170675831</v>
       </c>
       <c r="AJ3">
-        <v>0.5212953185498064</v>
+        <v>-2.624678663239076</v>
       </c>
       <c r="AK3">
-        <v>0.3906620944341862</v>
+        <v>-0.810961080222399</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="AM3">
-        <v>-0.006</v>
+        <v>0.001999999999999998</v>
       </c>
       <c r="AN3">
-        <v>4.419753086419753</v>
+        <v>0.2897435897435898</v>
+      </c>
+      <c r="AO3">
+        <v>60.00000000000001</v>
       </c>
       <c r="AP3">
-        <v>3.65679012345679</v>
+        <v>-0.8726495726495728</v>
       </c>
       <c r="AQ3">
-        <v>-46.5</v>
+        <v>540.0000000000005</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +850,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bank of Queensland Limited (ASX:BOQ)</t>
+          <t>MyState Limited (ASX:MYS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,13 +859,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0946</v>
+        <v>0.0555</v>
       </c>
       <c r="E4">
-        <v>0.0389</v>
-      </c>
-      <c r="F4">
-        <v>0.0679</v>
+        <v>0.0412</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -874,85 +877,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>292.5</v>
+        <v>25.6</v>
       </c>
       <c r="L4">
-        <v>0.256962136519371</v>
+        <v>0.2438095238095238</v>
       </c>
       <c r="M4">
-        <v>179.2</v>
+        <v>7.06</v>
       </c>
       <c r="N4">
-        <v>0.0587637317593048</v>
+        <v>0.02991525423728813</v>
       </c>
       <c r="O4">
-        <v>0.6126495726495726</v>
+        <v>0.27578125</v>
       </c>
       <c r="P4">
-        <v>167.5</v>
+        <v>7.06</v>
       </c>
       <c r="Q4">
-        <v>0.05492703721921627</v>
+        <v>0.02991525423728813</v>
       </c>
       <c r="R4">
-        <v>0.5726495726495726</v>
+        <v>0.27578125</v>
       </c>
       <c r="S4">
-        <v>11.69999999999999</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.06529017857142851</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1680.6</v>
+        <v>85</v>
       </c>
       <c r="V4">
-        <v>0.5511067388096409</v>
+        <v>0.3601694915254237</v>
       </c>
       <c r="W4">
-        <v>0.06459805653710247</v>
+        <v>0.08642808912896692</v>
       </c>
       <c r="X4">
-        <v>0.1331430917459325</v>
+        <v>0.1051195095160895</v>
       </c>
       <c r="Y4">
-        <v>-0.06854503520883005</v>
+        <v>-0.01869142038712257</v>
       </c>
       <c r="Z4">
-        <v>0.07069352064042131</v>
+        <v>0.0869277258051163</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05572302599774479</v>
+        <v>0.04266571210938518</v>
       </c>
       <c r="AC4">
-        <v>-0.05572302599774479</v>
+        <v>-0.04266571210938518</v>
       </c>
       <c r="AD4">
-        <v>14855.1</v>
+        <v>1323.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>14855.1</v>
+        <v>1323.6</v>
       </c>
       <c r="AG4">
-        <v>13174.5</v>
+        <v>1238.6</v>
       </c>
       <c r="AH4">
-        <v>0.8296806407291981</v>
+        <v>0.8486791484996152</v>
       </c>
       <c r="AI4">
-        <v>0.7639704596648942</v>
+        <v>0.8129721761562557</v>
       </c>
       <c r="AJ4">
-        <v>0.8120377218934911</v>
+        <v>0.8399565983995659</v>
       </c>
       <c r="AK4">
-        <v>0.7416403963071381</v>
+        <v>0.8026699501004472</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -969,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bendigo and Adelaide Bank Limited (ASX:BEN)</t>
+          <t>Auswide Bank Ltd (ASX:ABA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,13 +981,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0319</v>
+        <v>0.0796</v>
       </c>
       <c r="E5">
-        <v>0.0259</v>
-      </c>
-      <c r="F5">
-        <v>0.0361</v>
+        <v>0.0698</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -999,85 +999,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>336.3</v>
+        <v>16.7</v>
       </c>
       <c r="L5">
-        <v>0.2873867714920527</v>
+        <v>0.2477744807121662</v>
       </c>
       <c r="M5">
-        <v>153.19</v>
+        <v>5.13</v>
       </c>
       <c r="N5">
-        <v>0.04058013245033112</v>
+        <v>0.03158866995073892</v>
       </c>
       <c r="O5">
-        <v>0.4555159084151055</v>
+        <v>0.307185628742515</v>
       </c>
       <c r="P5">
-        <v>147.2</v>
+        <v>5.13</v>
       </c>
       <c r="Q5">
-        <v>0.0389933774834437</v>
+        <v>0.03158866995073892</v>
       </c>
       <c r="R5">
-        <v>0.4377044305679452</v>
+        <v>0.307185628742515</v>
       </c>
       <c r="S5">
-        <v>5.990000000000009</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.03910176904497688</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>2175.7</v>
+        <v>135.3</v>
       </c>
       <c r="V5">
-        <v>0.5763443708609272</v>
+        <v>0.833128078817734</v>
       </c>
       <c r="W5">
-        <v>0.07059934921801198</v>
+        <v>0.08594956253216675</v>
       </c>
       <c r="X5">
-        <v>0.09690456325371052</v>
+        <v>0.08754658280432098</v>
       </c>
       <c r="Y5">
-        <v>-0.02630521403569855</v>
+        <v>-0.001597020272154234</v>
       </c>
       <c r="Z5">
-        <v>0.120853472136159</v>
+        <v>0.1183078813410567</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05636643172894401</v>
+        <v>0.0433383513076606</v>
       </c>
       <c r="AC5">
-        <v>-0.05636643172894401</v>
+        <v>-0.0433383513076606</v>
       </c>
       <c r="AD5">
-        <v>9254.200000000001</v>
+        <v>608</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>9254.200000000001</v>
+        <v>608</v>
       </c>
       <c r="AG5">
-        <v>7078.500000000001</v>
+        <v>472.7</v>
       </c>
       <c r="AH5">
-        <v>0.7102661713689252</v>
+        <v>0.7892004153686397</v>
       </c>
       <c r="AI5">
-        <v>0.6667963627455219</v>
+        <v>0.7565953210552514</v>
       </c>
       <c r="AJ5">
-        <v>0.652185930805731</v>
+        <v>0.7442922374429223</v>
       </c>
       <c r="AK5">
-        <v>0.6048500798947269</v>
+        <v>0.7073170731707318</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1094,111 +1094,364 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Bank of Queensland Limited (ASX:BOQ)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.09390000000000001</v>
+      </c>
+      <c r="E6">
+        <v>-0.181</v>
+      </c>
+      <c r="F6">
+        <v>0.253</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>80.3</v>
+      </c>
+      <c r="L6">
+        <v>0.0732998630762209</v>
+      </c>
+      <c r="M6">
+        <v>160.6</v>
+      </c>
+      <c r="N6">
+        <v>0.05902892637924064</v>
+      </c>
+      <c r="O6">
+        <v>2</v>
+      </c>
+      <c r="P6">
+        <v>149.6</v>
+      </c>
+      <c r="Q6">
+        <v>0.05498584922997758</v>
+      </c>
+      <c r="R6">
+        <v>1.863013698630137</v>
+      </c>
+      <c r="S6">
+        <v>11</v>
+      </c>
+      <c r="T6">
+        <v>0.0684931506849315</v>
+      </c>
+      <c r="U6">
+        <v>1671.7</v>
+      </c>
+      <c r="V6">
+        <v>0.6144374609475504</v>
+      </c>
+      <c r="W6">
+        <v>0.01754117698457774</v>
+      </c>
+      <c r="X6">
+        <v>0.1002447883340849</v>
+      </c>
+      <c r="Y6">
+        <v>-0.08270361134950718</v>
+      </c>
+      <c r="Z6">
+        <v>0.06359683496171417</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.04699201416394396</v>
+      </c>
+      <c r="AC6">
+        <v>-0.04699201416394396</v>
+      </c>
+      <c r="AD6">
+        <v>13851.7</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>13851.7</v>
+      </c>
+      <c r="AG6">
+        <v>12180</v>
+      </c>
+      <c r="AH6">
+        <v>0.8358294513769882</v>
+      </c>
+      <c r="AI6">
+        <v>0.7772858377383477</v>
+      </c>
+      <c r="AJ6">
+        <v>0.8174112625581348</v>
+      </c>
+      <c r="AK6">
+        <v>0.754230938330165</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>BNK Banking Corporation Limited (ASX:BBC)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.218</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>41.2</v>
-      </c>
-      <c r="L6">
-        <v>5.651577503429356</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>-0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>-0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>96.5</v>
-      </c>
-      <c r="V6">
-        <v>2.275943396226415</v>
-      </c>
-      <c r="W6">
-        <v>0.429614181438999</v>
-      </c>
-      <c r="X6">
-        <v>0.1201653655760382</v>
-      </c>
-      <c r="Y6">
-        <v>0.3094488158629608</v>
-      </c>
-      <c r="Z6">
-        <v>0.07714285714285714</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.05694618049210187</v>
-      </c>
-      <c r="AC6">
-        <v>-0.05694618049210187</v>
-      </c>
-      <c r="AD6">
-        <v>169.8</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>169.8</v>
-      </c>
-      <c r="AG6">
-        <v>73.30000000000001</v>
-      </c>
-      <c r="AH6">
-        <v>0.8001885014137606</v>
-      </c>
-      <c r="AI6">
-        <v>0.5641196013289037</v>
-      </c>
-      <c r="AJ6">
-        <v>0.6335350043215212</v>
-      </c>
-      <c r="AK6">
-        <v>0.3584352078239609</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
+      <c r="D7">
+        <v>0.286</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>-2.62</v>
+      </c>
+      <c r="L7">
+        <v>-0.2201680672268908</v>
+      </c>
+      <c r="M7">
+        <v>39.5</v>
+      </c>
+      <c r="N7">
+        <v>1.282467532467533</v>
+      </c>
+      <c r="O7">
+        <v>-15.0763358778626</v>
+      </c>
+      <c r="P7">
+        <v>26.9</v>
+      </c>
+      <c r="Q7">
+        <v>0.8733766233766234</v>
+      </c>
+      <c r="R7">
+        <v>-10.26717557251908</v>
+      </c>
+      <c r="S7">
+        <v>12.6</v>
+      </c>
+      <c r="T7">
+        <v>0.3189873417721519</v>
+      </c>
+      <c r="U7">
+        <v>60.4</v>
+      </c>
+      <c r="V7">
+        <v>1.961038961038961</v>
+      </c>
+      <c r="W7">
+        <v>-0.01996951219512196</v>
+      </c>
+      <c r="X7">
+        <v>0.1104310987013538</v>
+      </c>
+      <c r="Y7">
+        <v>-0.1304006108964758</v>
+      </c>
+      <c r="Z7">
+        <v>0.05961625169079705</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.04764018343142462</v>
+      </c>
+      <c r="AC7">
+        <v>-0.04764018343142462</v>
+      </c>
+      <c r="AD7">
+        <v>190.1</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>190.1</v>
+      </c>
+      <c r="AG7">
+        <v>129.7</v>
+      </c>
+      <c r="AH7">
+        <v>0.860570393843368</v>
+      </c>
+      <c r="AI7">
+        <v>0.6902687000726216</v>
+      </c>
+      <c r="AJ7">
+        <v>0.8080996884735202</v>
+      </c>
+      <c r="AK7">
+        <v>0.6032558139534884</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bendigo and Adelaide Bank Limited (ASX:BEN)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0396</v>
+      </c>
+      <c r="E8">
+        <v>0.0272</v>
+      </c>
+      <c r="F8">
+        <v>-0.00398</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>330.8</v>
+      </c>
+      <c r="L8">
+        <v>0.2697765454248899</v>
+      </c>
+      <c r="M8">
+        <v>193.5</v>
+      </c>
+      <c r="N8">
+        <v>0.05187389416117098</v>
+      </c>
+      <c r="O8">
+        <v>0.5849455864570737</v>
+      </c>
+      <c r="P8">
+        <v>193.5</v>
+      </c>
+      <c r="Q8">
+        <v>0.05187389416117098</v>
+      </c>
+      <c r="R8">
+        <v>0.5849455864570737</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>4448.5</v>
+      </c>
+      <c r="V8">
+        <v>1.192563401426197</v>
+      </c>
+      <c r="W8">
+        <v>0.07153360435948448</v>
+      </c>
+      <c r="X8">
+        <v>0.07501899565901846</v>
+      </c>
+      <c r="Y8">
+        <v>-0.003485391299533971</v>
+      </c>
+      <c r="Z8">
+        <v>0.1151610206899143</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.04780364114369715</v>
+      </c>
+      <c r="AC8">
+        <v>-0.04780364114369715</v>
+      </c>
+      <c r="AD8">
+        <v>9006.799999999999</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>9006.799999999999</v>
+      </c>
+      <c r="AG8">
+        <v>4558.299999999999</v>
+      </c>
+      <c r="AH8">
+        <v>0.7071366883881605</v>
+      </c>
+      <c r="AI8">
+        <v>0.6639098354009567</v>
+      </c>
+      <c r="AJ8">
+        <v>0.5499547565904566</v>
+      </c>
+      <c r="AK8">
+        <v>0.4999341946522187</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/australia/australia_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,112 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07140000000000001</v>
+        <v>0.0633</v>
       </c>
       <c r="E2">
-        <v>0.0412</v>
+        <v>0.03386</v>
       </c>
       <c r="F2">
-        <v>0.12451</v>
+        <v>0.04485</v>
       </c>
       <c r="G2">
-        <v>0.0004662673505254474</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>0.0004662673505254474</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0004304006312542592</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0.0003111615736604396</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>451.386</v>
+        <v>556.5</v>
       </c>
       <c r="L2">
-        <v>0.1798859438327176</v>
+        <v>0.2418408587197427</v>
       </c>
       <c r="M2">
-        <v>405.896</v>
+        <v>400.53</v>
       </c>
       <c r="N2">
-        <v>0.05898356610685737</v>
+        <v>0.05472992361614036</v>
       </c>
       <c r="O2">
-        <v>0.8992215088638106</v>
+        <v>0.7197304582210242</v>
       </c>
       <c r="P2">
-        <v>382.296</v>
+        <v>387.9</v>
       </c>
       <c r="Q2">
-        <v>0.05555408623979331</v>
+        <v>0.05300411297705752</v>
       </c>
       <c r="R2">
-        <v>0.8469380973268997</v>
+        <v>0.6970350404312669</v>
       </c>
       <c r="S2">
-        <v>23.6</v>
+        <v>12.63</v>
       </c>
       <c r="T2">
-        <v>0.05814297258411022</v>
+        <v>0.03153321848550669</v>
       </c>
       <c r="U2">
-        <v>6402.26</v>
+        <v>3235.3</v>
       </c>
       <c r="V2">
-        <v>0.9303568548182014</v>
+        <v>0.4420835439924573</v>
       </c>
       <c r="W2">
-        <v>0.07874158344582562</v>
+        <v>0.06417423679437709</v>
       </c>
       <c r="X2">
-        <v>0.09389568556920296</v>
+        <v>0.08704696048524685</v>
       </c>
       <c r="Y2">
-        <v>-0.01515410212337734</v>
+        <v>-0.02287272369086976</v>
       </c>
       <c r="Z2">
-        <v>0.08405727347038969</v>
+        <v>0.09634886739521838</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04731609879768429</v>
+        <v>0.050608796827231</v>
       </c>
       <c r="AC2">
-        <v>-0.04516518273580228</v>
+        <v>-0.050608796827231</v>
       </c>
       <c r="AD2">
-        <v>24980.539</v>
+        <v>20565.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>24980.539</v>
+        <v>20565.3</v>
       </c>
       <c r="AG2">
-        <v>18578.279</v>
+        <v>17330</v>
       </c>
       <c r="AH2">
-        <v>0.7840217369573439</v>
+        <v>0.7375410635642456</v>
       </c>
       <c r="AI2">
-        <v>0.7326397670103303</v>
+        <v>0.7011359839625793</v>
       </c>
       <c r="AJ2">
-        <v>0.7297106429279521</v>
+        <v>0.703091085389256</v>
       </c>
       <c r="AK2">
-        <v>0.6708326052969849</v>
+        <v>0.6640839052578739</v>
       </c>
       <c r="AL2">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.001999999999999998</v>
-      </c>
-      <c r="AN2">
-        <v>21350.88803418804</v>
-      </c>
-      <c r="AO2">
-        <v>60.00000000000001</v>
-      </c>
-      <c r="AP2">
-        <v>15878.87094017094</v>
-      </c>
-      <c r="AQ2">
-        <v>540.0000000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Logan Community Financial Services Limited (NSX:LCB)</t>
+          <t>Bank of Queensland Limited (ASX:BOQ)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,121 +713,112 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.06320000000000001</v>
+        <v>0.08789999999999999</v>
       </c>
       <c r="E3">
-        <v>0.5</v>
+        <v>-0.008880000000000001</v>
+      </c>
+      <c r="F3">
+        <v>0.0555</v>
       </c>
       <c r="G3">
-        <v>0.3556231003039513</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.3556231003039513</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.3282674772036475</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.2483521737645573</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>0.606</v>
+        <v>192.9</v>
       </c>
       <c r="L3">
-        <v>0.1841945288753799</v>
+        <v>0.1820841986029828</v>
       </c>
       <c r="M3">
-        <v>0.106</v>
+        <v>159.12</v>
       </c>
       <c r="N3">
-        <v>0.075177304964539</v>
+        <v>0.05826650554762165</v>
       </c>
       <c r="O3">
-        <v>0.1749174917491749</v>
+        <v>0.8248833592534991</v>
       </c>
       <c r="P3">
-        <v>0.106</v>
+        <v>153.7</v>
       </c>
       <c r="Q3">
-        <v>0.075177304964539</v>
+        <v>0.05628181185689698</v>
       </c>
       <c r="R3">
-        <v>0.1749174917491749</v>
+        <v>0.7967858994297563</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>5.419999999999987</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.03406234288587223</v>
       </c>
       <c r="U3">
-        <v>1.36</v>
+        <v>1981.3</v>
       </c>
       <c r="V3">
-        <v>0.9645390070921988</v>
+        <v>0.7255117360577099</v>
       </c>
       <c r="W3">
-        <v>0.3293478260869565</v>
+        <v>0.04860288744992315</v>
       </c>
       <c r="X3">
-        <v>0.05452919371667127</v>
+        <v>0.1013193701998622</v>
       </c>
       <c r="Y3">
-        <v>0.2748186323702853</v>
+        <v>-0.05271648274993905</v>
       </c>
       <c r="Z3">
-        <v>2.141927083333333</v>
+        <v>0.06712795752068838</v>
       </c>
       <c r="AA3">
-        <v>0.5319522471910113</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05122207452287392</v>
+        <v>0.04945689837512987</v>
       </c>
       <c r="AC3">
-        <v>0.4807301726681374</v>
+        <v>-0.04945689837512987</v>
       </c>
       <c r="AD3">
-        <v>0.339</v>
+        <v>13178.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.339</v>
+        <v>13178.8</v>
       </c>
       <c r="AG3">
-        <v>-1.021</v>
+        <v>11197.5</v>
       </c>
       <c r="AH3">
-        <v>0.1938250428816467</v>
+        <v>0.8283500003142736</v>
       </c>
       <c r="AI3">
-        <v>0.1294387170675831</v>
+        <v>0.7639086935855969</v>
       </c>
       <c r="AJ3">
-        <v>-2.624678663239076</v>
+        <v>0.8039329714827259</v>
       </c>
       <c r="AK3">
-        <v>-0.810961080222399</v>
+        <v>0.7332765790249173</v>
       </c>
       <c r="AL3">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.001999999999999998</v>
-      </c>
-      <c r="AN3">
-        <v>0.2897435897435898</v>
-      </c>
-      <c r="AO3">
-        <v>60.00000000000001</v>
-      </c>
-      <c r="AP3">
-        <v>-0.8726495726495728</v>
-      </c>
-      <c r="AQ3">
-        <v>540.0000000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MyState Limited (ASX:MYS)</t>
+          <t>Bendigo and Adelaide Bank Limited (ASX:BEN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,10 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0555</v>
+        <v>0.0387</v>
       </c>
       <c r="E4">
-        <v>0.0412</v>
+        <v>0.0766</v>
+      </c>
+      <c r="F4">
+        <v>0.0342</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -877,581 +859,90 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>25.6</v>
+        <v>363.6</v>
       </c>
       <c r="L4">
-        <v>0.2438095238095238</v>
+        <v>0.2928243537086253</v>
       </c>
       <c r="M4">
-        <v>7.06</v>
+        <v>241.41</v>
       </c>
       <c r="N4">
-        <v>0.02991525423728813</v>
+        <v>0.0526245803723242</v>
       </c>
       <c r="O4">
-        <v>0.27578125</v>
+        <v>0.6639438943894389</v>
       </c>
       <c r="P4">
-        <v>7.06</v>
+        <v>234.2</v>
       </c>
       <c r="Q4">
-        <v>0.02991525423728813</v>
+        <v>0.05105288398657191</v>
       </c>
       <c r="R4">
-        <v>0.27578125</v>
+        <v>0.644114411441144</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>7.210000000000008</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.02986620272565349</v>
       </c>
       <c r="U4">
-        <v>85</v>
+        <v>1254</v>
       </c>
       <c r="V4">
-        <v>0.3601694915254237</v>
+        <v>0.2733574573832672</v>
       </c>
       <c r="W4">
-        <v>0.08642808912896692</v>
+        <v>0.07974558613883102</v>
       </c>
       <c r="X4">
-        <v>0.1051195095160895</v>
+        <v>0.0727745507706315</v>
       </c>
       <c r="Y4">
-        <v>-0.01869142038712257</v>
+        <v>0.006971035368199527</v>
       </c>
       <c r="Z4">
-        <v>0.0869277258051163</v>
+        <v>0.1532735890979114</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04266571210938518</v>
+        <v>0.05176069527933212</v>
       </c>
       <c r="AC4">
-        <v>-0.04266571210938518</v>
+        <v>-0.05176069527933212</v>
       </c>
       <c r="AD4">
-        <v>1323.6</v>
+        <v>7386.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1323.6</v>
+        <v>7386.5</v>
       </c>
       <c r="AG4">
-        <v>1238.6</v>
+        <v>6132.5</v>
       </c>
       <c r="AH4">
-        <v>0.8486791484996152</v>
+        <v>0.6168833880356442</v>
       </c>
       <c r="AI4">
-        <v>0.8129721761562557</v>
+        <v>0.6114854796516441</v>
       </c>
       <c r="AJ4">
-        <v>0.8399565983995659</v>
+        <v>0.5720669036091754</v>
       </c>
       <c r="AK4">
-        <v>0.8026699501004472</v>
+        <v>0.566481303576707</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Auswide Bank Ltd (ASX:ABA)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.0796</v>
-      </c>
-      <c r="E5">
-        <v>0.0698</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>16.7</v>
-      </c>
-      <c r="L5">
-        <v>0.2477744807121662</v>
-      </c>
-      <c r="M5">
-        <v>5.13</v>
-      </c>
-      <c r="N5">
-        <v>0.03158866995073892</v>
-      </c>
-      <c r="O5">
-        <v>0.307185628742515</v>
-      </c>
-      <c r="P5">
-        <v>5.13</v>
-      </c>
-      <c r="Q5">
-        <v>0.03158866995073892</v>
-      </c>
-      <c r="R5">
-        <v>0.307185628742515</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>135.3</v>
-      </c>
-      <c r="V5">
-        <v>0.833128078817734</v>
-      </c>
-      <c r="W5">
-        <v>0.08594956253216675</v>
-      </c>
-      <c r="X5">
-        <v>0.08754658280432098</v>
-      </c>
-      <c r="Y5">
-        <v>-0.001597020272154234</v>
-      </c>
-      <c r="Z5">
-        <v>0.1183078813410567</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.0433383513076606</v>
-      </c>
-      <c r="AC5">
-        <v>-0.0433383513076606</v>
-      </c>
-      <c r="AD5">
-        <v>608</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>608</v>
-      </c>
-      <c r="AG5">
-        <v>472.7</v>
-      </c>
-      <c r="AH5">
-        <v>0.7892004153686397</v>
-      </c>
-      <c r="AI5">
-        <v>0.7565953210552514</v>
-      </c>
-      <c r="AJ5">
-        <v>0.7442922374429223</v>
-      </c>
-      <c r="AK5">
-        <v>0.7073170731707318</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Bank of Queensland Limited (ASX:BOQ)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.09390000000000001</v>
-      </c>
-      <c r="E6">
-        <v>-0.181</v>
-      </c>
-      <c r="F6">
-        <v>0.253</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>80.3</v>
-      </c>
-      <c r="L6">
-        <v>0.0732998630762209</v>
-      </c>
-      <c r="M6">
-        <v>160.6</v>
-      </c>
-      <c r="N6">
-        <v>0.05902892637924064</v>
-      </c>
-      <c r="O6">
-        <v>2</v>
-      </c>
-      <c r="P6">
-        <v>149.6</v>
-      </c>
-      <c r="Q6">
-        <v>0.05498584922997758</v>
-      </c>
-      <c r="R6">
-        <v>1.863013698630137</v>
-      </c>
-      <c r="S6">
-        <v>11</v>
-      </c>
-      <c r="T6">
-        <v>0.0684931506849315</v>
-      </c>
-      <c r="U6">
-        <v>1671.7</v>
-      </c>
-      <c r="V6">
-        <v>0.6144374609475504</v>
-      </c>
-      <c r="W6">
-        <v>0.01754117698457774</v>
-      </c>
-      <c r="X6">
-        <v>0.1002447883340849</v>
-      </c>
-      <c r="Y6">
-        <v>-0.08270361134950718</v>
-      </c>
-      <c r="Z6">
-        <v>0.06359683496171417</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.04699201416394396</v>
-      </c>
-      <c r="AC6">
-        <v>-0.04699201416394396</v>
-      </c>
-      <c r="AD6">
-        <v>13851.7</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>13851.7</v>
-      </c>
-      <c r="AG6">
-        <v>12180</v>
-      </c>
-      <c r="AH6">
-        <v>0.8358294513769882</v>
-      </c>
-      <c r="AI6">
-        <v>0.7772858377383477</v>
-      </c>
-      <c r="AJ6">
-        <v>0.8174112625581348</v>
-      </c>
-      <c r="AK6">
-        <v>0.754230938330165</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BNK Banking Corporation Limited (ASX:BBC)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.286</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>-2.62</v>
-      </c>
-      <c r="L7">
-        <v>-0.2201680672268908</v>
-      </c>
-      <c r="M7">
-        <v>39.5</v>
-      </c>
-      <c r="N7">
-        <v>1.282467532467533</v>
-      </c>
-      <c r="O7">
-        <v>-15.0763358778626</v>
-      </c>
-      <c r="P7">
-        <v>26.9</v>
-      </c>
-      <c r="Q7">
-        <v>0.8733766233766234</v>
-      </c>
-      <c r="R7">
-        <v>-10.26717557251908</v>
-      </c>
-      <c r="S7">
-        <v>12.6</v>
-      </c>
-      <c r="T7">
-        <v>0.3189873417721519</v>
-      </c>
-      <c r="U7">
-        <v>60.4</v>
-      </c>
-      <c r="V7">
-        <v>1.961038961038961</v>
-      </c>
-      <c r="W7">
-        <v>-0.01996951219512196</v>
-      </c>
-      <c r="X7">
-        <v>0.1104310987013538</v>
-      </c>
-      <c r="Y7">
-        <v>-0.1304006108964758</v>
-      </c>
-      <c r="Z7">
-        <v>0.05961625169079705</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.04764018343142462</v>
-      </c>
-      <c r="AC7">
-        <v>-0.04764018343142462</v>
-      </c>
-      <c r="AD7">
-        <v>190.1</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>190.1</v>
-      </c>
-      <c r="AG7">
-        <v>129.7</v>
-      </c>
-      <c r="AH7">
-        <v>0.860570393843368</v>
-      </c>
-      <c r="AI7">
-        <v>0.6902687000726216</v>
-      </c>
-      <c r="AJ7">
-        <v>0.8080996884735202</v>
-      </c>
-      <c r="AK7">
-        <v>0.6032558139534884</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Bendigo and Adelaide Bank Limited (ASX:BEN)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.0396</v>
-      </c>
-      <c r="E8">
-        <v>0.0272</v>
-      </c>
-      <c r="F8">
-        <v>-0.00398</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>330.8</v>
-      </c>
-      <c r="L8">
-        <v>0.2697765454248899</v>
-      </c>
-      <c r="M8">
-        <v>193.5</v>
-      </c>
-      <c r="N8">
-        <v>0.05187389416117098</v>
-      </c>
-      <c r="O8">
-        <v>0.5849455864570737</v>
-      </c>
-      <c r="P8">
-        <v>193.5</v>
-      </c>
-      <c r="Q8">
-        <v>0.05187389416117098</v>
-      </c>
-      <c r="R8">
-        <v>0.5849455864570737</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>4448.5</v>
-      </c>
-      <c r="V8">
-        <v>1.192563401426197</v>
-      </c>
-      <c r="W8">
-        <v>0.07153360435948448</v>
-      </c>
-      <c r="X8">
-        <v>0.07501899565901846</v>
-      </c>
-      <c r="Y8">
-        <v>-0.003485391299533971</v>
-      </c>
-      <c r="Z8">
-        <v>0.1151610206899143</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.04780364114369715</v>
-      </c>
-      <c r="AC8">
-        <v>-0.04780364114369715</v>
-      </c>
-      <c r="AD8">
-        <v>9006.799999999999</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>9006.799999999999</v>
-      </c>
-      <c r="AG8">
-        <v>4558.299999999999</v>
-      </c>
-      <c r="AH8">
-        <v>0.7071366883881605</v>
-      </c>
-      <c r="AI8">
-        <v>0.6639098354009567</v>
-      </c>
-      <c r="AJ8">
-        <v>0.5499547565904566</v>
-      </c>
-      <c r="AK8">
-        <v>0.4999341946522187</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/australia/australia_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0633</v>
+        <v>0.0387</v>
       </c>
       <c r="E2">
-        <v>0.03386</v>
+        <v>0.008709999999999999</v>
       </c>
       <c r="F2">
         <v>0.04485</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>556.5</v>
+        <v>583.02</v>
       </c>
       <c r="L2">
-        <v>0.2418408587197427</v>
+        <v>0.2359640602234094</v>
       </c>
       <c r="M2">
-        <v>400.53</v>
+        <v>423.115</v>
       </c>
       <c r="N2">
-        <v>0.05472992361614036</v>
+        <v>0.05421354073238859</v>
       </c>
       <c r="O2">
-        <v>0.7197304582210242</v>
+        <v>0.7257298205893451</v>
       </c>
       <c r="P2">
-        <v>387.9</v>
+        <v>410.39</v>
       </c>
       <c r="Q2">
-        <v>0.05300411297705752</v>
+        <v>0.05258309202265331</v>
       </c>
       <c r="R2">
-        <v>0.6970350404312669</v>
+        <v>0.7039038111900107</v>
       </c>
       <c r="S2">
-        <v>12.63</v>
+        <v>12.72499999999999</v>
       </c>
       <c r="T2">
-        <v>0.03153321848550669</v>
+        <v>0.03007456601633125</v>
       </c>
       <c r="U2">
-        <v>3235.3</v>
+        <v>3540.3</v>
       </c>
       <c r="V2">
-        <v>0.4420835439924573</v>
+        <v>0.4536170976091024</v>
       </c>
       <c r="W2">
-        <v>0.06417423679437709</v>
+        <v>0.04860288744992315</v>
       </c>
       <c r="X2">
-        <v>0.08704696048524685</v>
+        <v>0.1012836761810804</v>
       </c>
       <c r="Y2">
-        <v>-0.02287272369086976</v>
+        <v>-0.05268078873115722</v>
       </c>
       <c r="Z2">
-        <v>0.09634886739521838</v>
+        <v>0.09419615506758007</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.050608796827231</v>
+        <v>0.04945077149681719</v>
       </c>
       <c r="AC2">
-        <v>-0.050608796827231</v>
+        <v>-0.04945077149681719</v>
       </c>
       <c r="AD2">
-        <v>20565.3</v>
+        <v>22916.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>20565.3</v>
+        <v>22916.1</v>
       </c>
       <c r="AG2">
-        <v>17330</v>
+        <v>19375.8</v>
       </c>
       <c r="AH2">
-        <v>0.7375410635642456</v>
+        <v>0.745949799320979</v>
       </c>
       <c r="AI2">
-        <v>0.7011359839625793</v>
+        <v>0.7102133792013388</v>
       </c>
       <c r="AJ2">
-        <v>0.703091085389256</v>
+        <v>0.7128592662359642</v>
       </c>
       <c r="AK2">
-        <v>0.6640839052578739</v>
+        <v>0.6744992376297596</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bank of Queensland Limited (ASX:BOQ)</t>
+          <t>MyState Limited (ASX:MYS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.08789999999999999</v>
+        <v>0.0463</v>
       </c>
       <c r="E3">
-        <v>-0.008880000000000001</v>
-      </c>
-      <c r="F3">
-        <v>0.0555</v>
+        <v>0.0263</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +731,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>192.9</v>
+        <v>23.5</v>
       </c>
       <c r="L3">
-        <v>0.1820841986029828</v>
+        <v>0.2329038652130822</v>
       </c>
       <c r="M3">
-        <v>159.12</v>
+        <v>14.8</v>
       </c>
       <c r="N3">
-        <v>0.05826650554762165</v>
+        <v>0.04833442194644024</v>
       </c>
       <c r="O3">
-        <v>0.8248833592534991</v>
+        <v>0.6297872340425532</v>
       </c>
       <c r="P3">
-        <v>153.7</v>
+        <v>14.8</v>
       </c>
       <c r="Q3">
-        <v>0.05628181185689698</v>
+        <v>0.04833442194644024</v>
       </c>
       <c r="R3">
-        <v>0.7967858994297563</v>
+        <v>0.6297872340425532</v>
       </c>
       <c r="S3">
-        <v>5.419999999999987</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.03406234288587223</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1981.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="V3">
-        <v>0.7255117360577099</v>
+        <v>0.2495101241018942</v>
       </c>
       <c r="W3">
-        <v>0.04860288744992315</v>
+        <v>0.07717569786535304</v>
       </c>
       <c r="X3">
-        <v>0.1013193701998622</v>
+        <v>0.103165033397864</v>
       </c>
       <c r="Y3">
-        <v>-0.05271648274993905</v>
+        <v>-0.02598933553251094</v>
       </c>
       <c r="Z3">
-        <v>0.06712795752068838</v>
+        <v>0.06728012269120492</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04945689837512987</v>
+        <v>0.04734087474384787</v>
       </c>
       <c r="AC3">
-        <v>-0.04945689837512987</v>
+        <v>-0.04734087474384787</v>
       </c>
       <c r="AD3">
-        <v>13178.8</v>
+        <v>1542.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>13178.8</v>
+        <v>1542.6</v>
       </c>
       <c r="AG3">
-        <v>11197.5</v>
+        <v>1466.2</v>
       </c>
       <c r="AH3">
-        <v>0.8283500003142736</v>
+        <v>0.8343790566854176</v>
       </c>
       <c r="AI3">
-        <v>0.7639086935855969</v>
+        <v>0.8325777202072538</v>
       </c>
       <c r="AJ3">
-        <v>0.8039329714827259</v>
+        <v>0.8272399006996163</v>
       </c>
       <c r="AK3">
-        <v>0.7332765790249173</v>
+        <v>0.825377167304661</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,120 +826,483 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>BNK Banking Corporation Limited (ASX:BBC)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.0716</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>-4.47</v>
+      </c>
+      <c r="L4">
+        <v>-0.3215827338129496</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>79</v>
+      </c>
+      <c r="V4">
+        <v>3.211382113821138</v>
+      </c>
+      <c r="W4">
+        <v>-0.05240328253223916</v>
+      </c>
+      <c r="X4">
+        <v>0.1386021400519558</v>
+      </c>
+      <c r="Y4">
+        <v>-0.191005422584195</v>
+      </c>
+      <c r="Z4">
+        <v>0.06610548342607125</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.0486668340570426</v>
+      </c>
+      <c r="AC4">
+        <v>-0.0486668340570426</v>
+      </c>
+      <c r="AD4">
+        <v>222.2</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>222.2</v>
+      </c>
+      <c r="AG4">
+        <v>143.2</v>
+      </c>
+      <c r="AH4">
+        <v>0.9003241491085899</v>
+      </c>
+      <c r="AI4">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="AJ4">
+        <v>0.8533969010727056</v>
+      </c>
+      <c r="AK4">
+        <v>0.6392857142857142</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bank of Queensland Limited (ASX:BOQ)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.08789999999999999</v>
+      </c>
+      <c r="E5">
+        <v>-0.008880000000000001</v>
+      </c>
+      <c r="F5">
+        <v>0.0555</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>192.9</v>
+      </c>
+      <c r="L5">
+        <v>0.1820841986029828</v>
+      </c>
+      <c r="M5">
+        <v>159.12</v>
+      </c>
+      <c r="N5">
+        <v>0.05826650554762165</v>
+      </c>
+      <c r="O5">
+        <v>0.8248833592534991</v>
+      </c>
+      <c r="P5">
+        <v>153.7</v>
+      </c>
+      <c r="Q5">
+        <v>0.05628181185689698</v>
+      </c>
+      <c r="R5">
+        <v>0.7967858994297563</v>
+      </c>
+      <c r="S5">
+        <v>5.419999999999987</v>
+      </c>
+      <c r="T5">
+        <v>0.03406234288587223</v>
+      </c>
+      <c r="U5">
+        <v>1981.3</v>
+      </c>
+      <c r="V5">
+        <v>0.7255117360577099</v>
+      </c>
+      <c r="W5">
+        <v>0.04860288744992315</v>
+      </c>
+      <c r="X5">
+        <v>0.1012836761810804</v>
+      </c>
+      <c r="Y5">
+        <v>-0.05268078873115722</v>
+      </c>
+      <c r="Z5">
+        <v>0.06712795752068838</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.04945077149681719</v>
+      </c>
+      <c r="AC5">
+        <v>-0.04945077149681719</v>
+      </c>
+      <c r="AD5">
+        <v>13178.8</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>13178.8</v>
+      </c>
+      <c r="AG5">
+        <v>11197.5</v>
+      </c>
+      <c r="AH5">
+        <v>0.8283500003142736</v>
+      </c>
+      <c r="AI5">
+        <v>0.7639086935855969</v>
+      </c>
+      <c r="AJ5">
+        <v>0.8039329714827259</v>
+      </c>
+      <c r="AK5">
+        <v>0.7332765790249173</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Auswide Bank Ltd (ASX:ABA)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.0286</v>
+      </c>
+      <c r="E6">
+        <v>-0.08169999999999999</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>7.49</v>
+      </c>
+      <c r="L6">
+        <v>0.1364298724954463</v>
+      </c>
+      <c r="M6">
+        <v>7.785</v>
+      </c>
+      <c r="N6">
+        <v>0.05006430868167203</v>
+      </c>
+      <c r="O6">
+        <v>1.039385847797063</v>
+      </c>
+      <c r="P6">
+        <v>7.69</v>
+      </c>
+      <c r="Q6">
+        <v>0.04945337620578778</v>
+      </c>
+      <c r="R6">
+        <v>1.026702269692924</v>
+      </c>
+      <c r="S6">
+        <v>0.09499999999999975</v>
+      </c>
+      <c r="T6">
+        <v>0.01220295439948616</v>
+      </c>
+      <c r="U6">
+        <v>149.6</v>
+      </c>
+      <c r="V6">
+        <v>0.9620578778135048</v>
+      </c>
+      <c r="W6">
+        <v>0.03829243353783231</v>
+      </c>
+      <c r="X6">
+        <v>0.09190401261447702</v>
+      </c>
+      <c r="Y6">
+        <v>-0.0536115790766447</v>
+      </c>
+      <c r="Z6">
+        <v>0.08613115782867901</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.05124832631362262</v>
+      </c>
+      <c r="AC6">
+        <v>-0.05124832631362262</v>
+      </c>
+      <c r="AD6">
+        <v>586</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>586</v>
+      </c>
+      <c r="AG6">
+        <v>436.4</v>
+      </c>
+      <c r="AH6">
+        <v>0.7902899527983817</v>
+      </c>
+      <c r="AI6">
+        <v>0.751956884383421</v>
+      </c>
+      <c r="AJ6">
+        <v>0.7372867038351073</v>
+      </c>
+      <c r="AK6">
+        <v>0.6930284262347148</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Bendigo and Adelaide Bank Limited (ASX:BEN)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D7">
         <v>0.0387</v>
       </c>
-      <c r="E4">
+      <c r="E7">
         <v>0.0766</v>
       </c>
-      <c r="F4">
+      <c r="F7">
         <v>0.0342</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>363.6</v>
       </c>
-      <c r="L4">
+      <c r="L7">
         <v>0.2928243537086253</v>
       </c>
-      <c r="M4">
+      <c r="M7">
         <v>241.41</v>
       </c>
-      <c r="N4">
+      <c r="N7">
         <v>0.0526245803723242</v>
       </c>
-      <c r="O4">
+      <c r="O7">
         <v>0.6639438943894389</v>
       </c>
-      <c r="P4">
+      <c r="P7">
         <v>234.2</v>
       </c>
-      <c r="Q4">
+      <c r="Q7">
         <v>0.05105288398657191</v>
       </c>
-      <c r="R4">
+      <c r="R7">
         <v>0.644114411441144</v>
       </c>
-      <c r="S4">
+      <c r="S7">
         <v>7.210000000000008</v>
       </c>
-      <c r="T4">
+      <c r="T7">
         <v>0.02986620272565349</v>
       </c>
-      <c r="U4">
+      <c r="U7">
         <v>1254</v>
       </c>
-      <c r="V4">
+      <c r="V7">
         <v>0.2733574573832672</v>
       </c>
-      <c r="W4">
+      <c r="W7">
         <v>0.07974558613883102</v>
       </c>
-      <c r="X4">
-        <v>0.0727745507706315</v>
-      </c>
-      <c r="Y4">
-        <v>0.006971035368199527</v>
-      </c>
-      <c r="Z4">
+      <c r="X7">
+        <v>0.07275720853280761</v>
+      </c>
+      <c r="Y7">
+        <v>0.006988377606023416</v>
+      </c>
+      <c r="Z7">
         <v>0.1532735890979114</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.05176069527933212</v>
-      </c>
-      <c r="AC4">
-        <v>-0.05176069527933212</v>
-      </c>
-      <c r="AD4">
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.05175405117993316</v>
+      </c>
+      <c r="AC7">
+        <v>-0.05175405117993316</v>
+      </c>
+      <c r="AD7">
         <v>7386.5</v>
       </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
         <v>7386.5</v>
       </c>
-      <c r="AG4">
+      <c r="AG7">
         <v>6132.5</v>
       </c>
-      <c r="AH4">
+      <c r="AH7">
         <v>0.6168833880356442</v>
       </c>
-      <c r="AI4">
+      <c r="AI7">
         <v>0.6114854796516441</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ7">
         <v>0.5720669036091754</v>
       </c>
-      <c r="AK4">
+      <c r="AK7">
         <v>0.566481303576707</v>
       </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
         <v>0</v>
       </c>
     </row>
